--- a/InputData/fuels/MPIiFE/Max Perc Inc in Fuel Exports.xlsx
+++ b/InputData/fuels/MPIiFE/Max Perc Inc in Fuel Exports.xlsx
@@ -1,21 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21929"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deept\Dropbox\EPS\Input Data for India 2.0\fuels\MPIiFE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox (Energy Innovation)\EI-PlcyMdl\eps-1.5.0-us-wipM\InputData\fuels\MPIiFE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A59D8C38-AA94-4242-8F7C-A233E9586D0D}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28185" windowHeight="12510"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="India Trends" sheetId="3" r:id="rId2"/>
-    <sheet name="MPIiFE" sheetId="2" r:id="rId3"/>
+    <sheet name="MPIiFE" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,12 +25,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>MPIiFE Maximum Percentage Increase in Fuel Exports</t>
   </si>
   <si>
     <t>Source:</t>
+  </si>
+  <si>
+    <t>none needed for U.S.</t>
   </si>
   <si>
     <t>Notes</t>
@@ -148,182 +149,23 @@
     </r>
   </si>
   <si>
+    <t>For the U.S., we do not wish to impose a cap (we limit</t>
+  </si>
+  <si>
+    <t>changes in exports using fuels/PoFDCtAE), so we pick</t>
+  </si>
+  <si>
+    <t>an arbitrarily high percentage.</t>
+  </si>
+  <si>
     <t>Alternatively, it may represent a legislative cap on exports.</t>
-  </si>
-  <si>
-    <t>http://www.mospi.gov.in/sites/default/files/publication_reports/Energy%20Statistics%202019-finall.pdf</t>
-  </si>
-  <si>
-    <t>Energy Statistics 2019</t>
-  </si>
-  <si>
-    <t>Table 4.1: Trends of Foreign Trade in Coal, Crude Oil,  Petroleum Products, Natural Gas and Electricity in India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                   (Million Tonnes)</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Coal</t>
-  </si>
-  <si>
-    <t>Crude Oil</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
-  </si>
-  <si>
-    <t>Natural Gas (Billion Cubic Metres)</t>
-  </si>
-  <si>
-    <t>Electricity(Gwh)</t>
-  </si>
-  <si>
-    <t>Gross</t>
-  </si>
-  <si>
-    <t>Exports</t>
-  </si>
-  <si>
-    <t>Net</t>
-  </si>
-  <si>
-    <t>Imports</t>
-  </si>
-  <si>
-    <t>4=(2)-(3)</t>
-  </si>
-  <si>
-    <t>7=(5)-(6)</t>
-  </si>
-  <si>
-    <t>10=(8)-(9)</t>
-  </si>
-  <si>
-    <t>13= (11)-(12)</t>
-  </si>
-  <si>
-    <t>16= (14)-(15)</t>
-  </si>
-  <si>
-    <t>2008-09</t>
-  </si>
-  <si>
-    <t>2009-10</t>
-  </si>
-  <si>
-    <t>2010-11</t>
-  </si>
-  <si>
-    <t>2011-12</t>
-  </si>
-  <si>
-    <t>2012-13</t>
-  </si>
-  <si>
-    <t>2013-14</t>
-  </si>
-  <si>
-    <t>2014-15</t>
-  </si>
-  <si>
-    <t>2015-16</t>
-  </si>
-  <si>
-    <t>2016-17</t>
-  </si>
-  <si>
-    <t>2017-18 (P)</t>
-  </si>
-  <si>
-    <t>Growth rate of 2017-18 over 2016-17(%)</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>CAGR 2008-09 to 2017-18 (%)</t>
-  </si>
-  <si>
-    <t>Source: Energy Statistics 2019</t>
-  </si>
-  <si>
-    <t>Table 4.1; Page 46</t>
-  </si>
-  <si>
-    <t>For India, in the historic trends from 2008-09 to 2017-19,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">there is a net positive CAGR in exports for petroleum products </t>
-  </si>
-  <si>
-    <t xml:space="preserve">and electricity. In case of petroleum products, this is because </t>
-  </si>
-  <si>
-    <t xml:space="preserve">of value addition to imported crude oil. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">In the case of coal, there is a net negative CAGR in the same </t>
-  </si>
-  <si>
-    <t xml:space="preserve">concern in the recent years, with decline in plant performance due </t>
-  </si>
-  <si>
-    <t xml:space="preserve">domestic coal production. Hence, it is not considered feasible for exports </t>
-  </si>
-  <si>
-    <t>the presence of a roadmap to reduce oil import dependence.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">due to domestic shortages. MoPnG has communicated  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Various policy announcements to reduce fuel import dependence and </t>
-  </si>
-  <si>
-    <t>Hence, it is not relevant/necessary to impose a cap on fuel exports</t>
-  </si>
-  <si>
-    <t>period. Coal supplies for thermal power plants have been a cause for</t>
-  </si>
-  <si>
-    <t>to grow significantly in the sector. There are no natural gas and crude oil exports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boost domestic production (e.g. Make in India), along with exemption of </t>
-  </si>
-  <si>
-    <t xml:space="preserve">taxes on export of fuels imply a focus towards increasing exports in the </t>
-  </si>
-  <si>
-    <t xml:space="preserve">medium to long-term. Based on recent trends, growth in exports is still </t>
-  </si>
-  <si>
-    <t xml:space="preserve">building slowly in the sectors with a net positive CAGR in the past decade. </t>
-  </si>
-  <si>
-    <t>in India and we pick an arbitrarily high percentage.</t>
-  </si>
-  <si>
-    <t>Ministry of Statistics and Programme Implementation</t>
-  </si>
-  <si>
-    <t>Table 4.1, Page 46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">to shortage of coal. Imports have been on rise, with not much increase in </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -339,79 +181,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color indexed="8"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -424,26 +195,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="16">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -451,181 +204,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -641,165 +224,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="11" fillId="4" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1077,12 +503,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B40"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="93.42578125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1093,168 +516,68 @@
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="54" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="53">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>86</v>
+      <c r="B3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1264,843 +587,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E3928E-A87D-4009-A134-F1B3E64D6DAF}">
-  <dimension ref="A1:P22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" customWidth="1"/>
-    <col min="13" max="13" width="13.28515625" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="N2" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="O2" s="9"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="56" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="57"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="59" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" s="60"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" s="60"/>
-      <c r="J3" s="61"/>
-      <c r="K3" s="62" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" s="60"/>
-      <c r="M3" s="61"/>
-      <c r="N3" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="O3" s="59"/>
-      <c r="P3" s="61"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="L4" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="M4" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="N4" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="O4" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="P4" s="15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="17"/>
-      <c r="J5" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="L5" s="17"/>
-      <c r="M5" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N5" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="O5" s="17"/>
-      <c r="P5" s="21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="24">
-        <v>1</v>
-      </c>
-      <c r="B6" s="24">
-        <v>2</v>
-      </c>
-      <c r="C6" s="25">
-        <v>3</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="27">
-        <v>5</v>
-      </c>
-      <c r="F6" s="25">
-        <v>6</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="29">
-        <v>8</v>
-      </c>
-      <c r="I6" s="30">
-        <v>9</v>
-      </c>
-      <c r="J6" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="K6" s="25">
-        <v>11</v>
-      </c>
-      <c r="L6" s="25">
-        <v>12</v>
-      </c>
-      <c r="M6" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="N6" s="25">
-        <v>14</v>
-      </c>
-      <c r="O6" s="25">
-        <v>15</v>
-      </c>
-      <c r="P6" s="25" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="33">
-        <v>59.003143000000001</v>
-      </c>
-      <c r="C7" s="34">
-        <v>1.6554349999999998</v>
-      </c>
-      <c r="D7" s="35">
-        <v>57.347999999999999</v>
-      </c>
-      <c r="E7" s="36">
-        <v>132.77500000000001</v>
-      </c>
-      <c r="F7" s="34">
-        <v>0</v>
-      </c>
-      <c r="G7" s="34">
-        <v>132.77500000000001</v>
-      </c>
-      <c r="H7" s="36">
-        <v>18.585999999999999</v>
-      </c>
-      <c r="I7" s="34">
-        <v>38.944000000000003</v>
-      </c>
-      <c r="J7" s="37">
-        <v>-20.358000000000004</v>
-      </c>
-      <c r="K7" s="34">
-        <v>8.06</v>
-      </c>
-      <c r="L7" s="34">
-        <v>0</v>
-      </c>
-      <c r="M7" s="34">
-        <v>8.06</v>
-      </c>
-      <c r="N7" s="38">
-        <v>5896.79</v>
-      </c>
-      <c r="O7" s="38">
-        <v>58.47</v>
-      </c>
-      <c r="P7" s="38">
-        <v>5838.32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="33">
-        <v>73.254999999999995</v>
-      </c>
-      <c r="C8" s="34">
-        <v>2.4540000000000002</v>
-      </c>
-      <c r="D8" s="35">
-        <v>70.805000000000007</v>
-      </c>
-      <c r="E8" s="36">
-        <v>159.25920000000002</v>
-      </c>
-      <c r="F8" s="34">
-        <v>0</v>
-      </c>
-      <c r="G8" s="34">
-        <v>159.25920000000002</v>
-      </c>
-      <c r="H8" s="36">
-        <v>14.664999999999999</v>
-      </c>
-      <c r="I8" s="34">
-        <v>51.15</v>
-      </c>
-      <c r="J8" s="37">
-        <v>-36.484999999999999</v>
-      </c>
-      <c r="K8" s="34">
-        <v>9.1484018200000001</v>
-      </c>
-      <c r="L8" s="34">
-        <v>0</v>
-      </c>
-      <c r="M8" s="34">
-        <v>9.1484018200000001</v>
-      </c>
-      <c r="N8" s="38">
-        <v>5358.57</v>
-      </c>
-      <c r="O8" s="38">
-        <v>104.97</v>
-      </c>
-      <c r="P8" s="38">
-        <v>5253.5999999999995</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="33">
-        <v>68.917597999999998</v>
-      </c>
-      <c r="C9" s="34">
-        <v>1.88</v>
-      </c>
-      <c r="D9" s="35">
-        <v>67.043000000000006</v>
-      </c>
-      <c r="E9" s="36">
-        <v>163.595</v>
-      </c>
-      <c r="F9" s="34">
-        <v>0</v>
-      </c>
-      <c r="G9" s="34">
-        <v>163.595</v>
-      </c>
-      <c r="H9" s="36">
-        <v>17.379441280999998</v>
-      </c>
-      <c r="I9" s="34">
-        <v>59.077092999999998</v>
-      </c>
-      <c r="J9" s="37">
-        <v>-41.697651719</v>
-      </c>
-      <c r="K9" s="39">
-        <v>9.9312479920000012</v>
-      </c>
-      <c r="L9" s="34">
-        <v>0</v>
-      </c>
-      <c r="M9" s="34">
-        <v>9.9312479920000012</v>
-      </c>
-      <c r="N9" s="38">
-        <v>5610.92</v>
-      </c>
-      <c r="O9" s="38">
-        <v>128.46</v>
-      </c>
-      <c r="P9" s="38">
-        <v>5482.46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="33">
-        <v>102.85262600000003</v>
-      </c>
-      <c r="C10" s="40">
-        <v>2.02</v>
-      </c>
-      <c r="D10" s="35">
-        <v>100.839</v>
-      </c>
-      <c r="E10" s="36">
-        <v>171.729154097221</v>
-      </c>
-      <c r="F10" s="34">
-        <v>0</v>
-      </c>
-      <c r="G10" s="34">
-        <v>171.729154097221</v>
-      </c>
-      <c r="H10" s="36">
-        <v>15.849370446253001</v>
-      </c>
-      <c r="I10" s="34">
-        <v>60.837340519999998</v>
-      </c>
-      <c r="J10" s="37">
-        <v>-44.987970073746993</v>
-      </c>
-      <c r="K10" s="39">
-        <v>13.214450363387753</v>
-      </c>
-      <c r="L10" s="34">
-        <v>0</v>
-      </c>
-      <c r="M10" s="34">
-        <v>13.214450363387753</v>
-      </c>
-      <c r="N10" s="38">
-        <v>5252.7</v>
-      </c>
-      <c r="O10" s="38">
-        <v>134.75</v>
-      </c>
-      <c r="P10" s="38">
-        <v>5117.95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="41">
-        <v>145.785</v>
-      </c>
-      <c r="C11" s="42">
-        <v>2.4430000000000001</v>
-      </c>
-      <c r="D11" s="35">
-        <v>143.34199999999998</v>
-      </c>
-      <c r="E11" s="36">
-        <v>184.79524788937999</v>
-      </c>
-      <c r="F11" s="34">
-        <v>0</v>
-      </c>
-      <c r="G11" s="34">
-        <v>184.79524788937999</v>
-      </c>
-      <c r="H11" s="43">
-        <v>16.354119653000001</v>
-      </c>
-      <c r="I11" s="34">
-        <v>63.407761975930008</v>
-      </c>
-      <c r="J11" s="37">
-        <v>-47.053642322930003</v>
-      </c>
-      <c r="K11" s="39">
-        <v>13.135545616612244</v>
-      </c>
-      <c r="L11" s="34">
-        <v>0</v>
-      </c>
-      <c r="M11" s="34">
-        <v>13.135545616612244</v>
-      </c>
-      <c r="N11" s="38">
-        <v>4794.5</v>
-      </c>
-      <c r="O11" s="38">
-        <v>153.53</v>
-      </c>
-      <c r="P11" s="38">
-        <v>4640.97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" s="41">
-        <v>166.857</v>
-      </c>
-      <c r="C12" s="42">
-        <v>2.1880000000000002</v>
-      </c>
-      <c r="D12" s="35">
-        <v>164.66900000000001</v>
-      </c>
-      <c r="E12" s="36">
-        <v>189.23820178337502</v>
-      </c>
-      <c r="F12" s="34">
-        <v>0</v>
-      </c>
-      <c r="G12" s="34">
-        <v>189.23820178337502</v>
-      </c>
-      <c r="H12" s="43">
-        <v>16.697004688</v>
-      </c>
-      <c r="I12" s="34">
-        <v>67.864014699800009</v>
-      </c>
-      <c r="J12" s="37">
-        <v>-51.167010011800009</v>
-      </c>
-      <c r="K12" s="39">
-        <v>12.994543592530611</v>
-      </c>
-      <c r="L12" s="34">
-        <v>0</v>
-      </c>
-      <c r="M12" s="34">
-        <v>12.994543592530611</v>
-      </c>
-      <c r="N12" s="38">
-        <v>5597.9</v>
-      </c>
-      <c r="O12" s="38">
-        <v>1651</v>
-      </c>
-      <c r="P12" s="38">
-        <v>3946.8999999999996</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" s="41">
-        <v>212.10300000000001</v>
-      </c>
-      <c r="C13" s="42">
-        <v>1.238</v>
-      </c>
-      <c r="D13" s="35">
-        <v>210.86500000000001</v>
-      </c>
-      <c r="E13" s="36">
-        <v>189.43485654402394</v>
-      </c>
-      <c r="F13" s="34">
-        <v>0</v>
-      </c>
-      <c r="G13" s="34">
-        <v>189.43485654402394</v>
-      </c>
-      <c r="H13" s="43">
-        <v>21.301161557</v>
-      </c>
-      <c r="I13" s="34">
-        <v>63.931857026299994</v>
-      </c>
-      <c r="J13" s="37">
-        <v>-42.630695469299994</v>
-      </c>
-      <c r="K13" s="39">
-        <v>14.092325757755102</v>
-      </c>
-      <c r="L13" s="34">
-        <v>0</v>
-      </c>
-      <c r="M13" s="34">
-        <v>14.092325757755102</v>
-      </c>
-      <c r="N13" s="38">
-        <v>5007.74</v>
-      </c>
-      <c r="O13" s="38">
-        <v>4432.7602800000004</v>
-      </c>
-      <c r="P13" s="38">
-        <v>574.97971999999936</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="41">
-        <v>203.94900000000001</v>
-      </c>
-      <c r="C14" s="42">
-        <v>1.575</v>
-      </c>
-      <c r="D14" s="35">
-        <v>202.37400000000002</v>
-      </c>
-      <c r="E14" s="36">
-        <v>202.85049173136341</v>
-      </c>
-      <c r="F14" s="34">
-        <v>0</v>
-      </c>
-      <c r="G14" s="34">
-        <v>202.85049173136341</v>
-      </c>
-      <c r="H14" s="43">
-        <v>29.455754196099996</v>
-      </c>
-      <c r="I14" s="34">
-        <v>60.538562213000006</v>
-      </c>
-      <c r="J14" s="37">
-        <v>-31.08280801690001</v>
-      </c>
-      <c r="K14" s="39">
-        <v>16.142088786971119</v>
-      </c>
-      <c r="L14" s="34">
-        <v>0</v>
-      </c>
-      <c r="M14" s="34">
-        <v>16.142088786971119</v>
-      </c>
-      <c r="N14" s="38">
-        <v>5244.21</v>
-      </c>
-      <c r="O14" s="38">
-        <v>5150.3000452999995</v>
-      </c>
-      <c r="P14" s="38">
-        <v>93.909954700000526</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="44">
-        <v>190.953</v>
-      </c>
-      <c r="C15" s="42">
-        <v>1.7729999999999999</v>
-      </c>
-      <c r="D15" s="35">
-        <v>189.18</v>
-      </c>
-      <c r="E15" s="36">
-        <v>213.93182953023481</v>
-      </c>
-      <c r="F15" s="34">
-        <v>0</v>
-      </c>
-      <c r="G15" s="34">
-        <v>213.93182953023481</v>
-      </c>
-      <c r="H15" s="43">
-        <v>36.287225948000007</v>
-      </c>
-      <c r="I15" s="34">
-        <v>65.51346949068099</v>
-      </c>
-      <c r="J15" s="37">
-        <v>-29.226243542680983</v>
-      </c>
-      <c r="K15" s="39">
-        <v>18.631137717102039</v>
-      </c>
-      <c r="L15" s="34">
-        <v>0</v>
-      </c>
-      <c r="M15" s="34">
-        <v>18.631137717102039</v>
-      </c>
-      <c r="N15" s="38">
-        <v>5617.3</v>
-      </c>
-      <c r="O15" s="38">
-        <v>6710.1867269999993</v>
-      </c>
-      <c r="P15" s="38">
-        <v>-1092.8867269999992</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" s="44">
-        <v>208.273</v>
-      </c>
-      <c r="C16" s="45">
-        <v>1.5029999999999999</v>
-      </c>
-      <c r="D16" s="35">
-        <v>206.77</v>
-      </c>
-      <c r="E16" s="46">
-        <v>220.43279203083119</v>
-      </c>
-      <c r="F16" s="46">
-        <v>0</v>
-      </c>
-      <c r="G16" s="46">
-        <v>220.43279203083119</v>
-      </c>
-      <c r="H16" s="43">
-        <v>35.460834880927038</v>
-      </c>
-      <c r="I16" s="46">
-        <v>66.832729412250004</v>
-      </c>
-      <c r="J16" s="37">
-        <v>-31.371894531322965</v>
-      </c>
-      <c r="K16" s="36">
-        <v>19.869855000000001</v>
-      </c>
-      <c r="L16" s="34">
-        <v>0</v>
-      </c>
-      <c r="M16" s="34">
-        <v>19.869855000000001</v>
-      </c>
-      <c r="N16" s="47">
-        <v>5611.14</v>
-      </c>
-      <c r="O16" s="47">
-        <v>7202.86</v>
-      </c>
-      <c r="P16" s="38">
-        <v>-1591.7199999999993</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A17" s="48" t="s">
-        <v>62</v>
-      </c>
-      <c r="B17" s="49">
-        <v>9.0702947845804953</v>
-      </c>
-      <c r="C17" s="49">
-        <v>-15.228426395939088</v>
-      </c>
-      <c r="D17" s="49">
-        <v>9.2980230468337055</v>
-      </c>
-      <c r="E17" s="49">
-        <v>3.0388009651820469</v>
-      </c>
-      <c r="F17" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="G17" s="49">
-        <v>3.0388009651820469</v>
-      </c>
-      <c r="H17" s="49">
-        <v>-2.2773608218418131</v>
-      </c>
-      <c r="I17" s="49">
-        <v>2.0137231806303171</v>
-      </c>
-      <c r="J17" s="49">
-        <v>7.3415216208287211</v>
-      </c>
-      <c r="K17" s="49">
-        <v>6.6486400439244742</v>
-      </c>
-      <c r="L17" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="M17" s="49">
-        <v>6.6486400439244742</v>
-      </c>
-      <c r="N17" s="50">
-        <v>-0.10966122514374974</v>
-      </c>
-      <c r="O17" s="50">
-        <v>7.342169347055794</v>
-      </c>
-      <c r="P17" s="50">
-        <v>45.643639059402773</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="B18" s="49">
-        <v>13.44249840166154</v>
-      </c>
-      <c r="C18" s="52">
-        <v>-0.96135617398737105</v>
-      </c>
-      <c r="D18" s="49">
-        <v>13.68336630813689</v>
-      </c>
-      <c r="E18" s="49">
-        <v>5.2000603944617918</v>
-      </c>
-      <c r="F18" s="52" t="s">
-        <v>63</v>
-      </c>
-      <c r="G18" s="49">
-        <v>5.2000603944617918</v>
-      </c>
-      <c r="H18" s="49">
-        <v>6.6734404727747609</v>
-      </c>
-      <c r="I18" s="52">
-        <v>5.5491801113085826</v>
-      </c>
-      <c r="J18" s="49">
-        <v>4.4192485807056148</v>
-      </c>
-      <c r="K18" s="49">
-        <v>9.4424900479599181</v>
-      </c>
-      <c r="L18" s="52"/>
-      <c r="M18" s="49">
-        <v>9.4424900479599181</v>
-      </c>
-      <c r="N18" s="49">
-        <v>-0.49531154281768908</v>
-      </c>
-      <c r="O18" s="52">
-        <v>61.829312074429652</v>
-      </c>
-      <c r="P18" s="49"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="51" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="51" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="51" t="s">
-        <v>66</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
@@ -2112,7 +599,7 @@
   <sheetData>
     <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="3">
         <v>2017</v>
@@ -2219,7 +706,7 @@
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="6">
         <v>0</v>
@@ -2326,7 +813,7 @@
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>999</v>
@@ -2433,7 +920,7 @@
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>999</v>
@@ -2540,7 +1027,7 @@
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>999</v>
@@ -2647,7 +1134,7 @@
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="6">
         <v>0</v>
@@ -2754,7 +1241,7 @@
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="6">
         <v>0</v>
@@ -2861,7 +1348,7 @@
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="6">
         <v>0</v>
@@ -2968,7 +1455,7 @@
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>999</v>
@@ -3075,7 +1562,7 @@
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>999</v>
@@ -3182,7 +1669,7 @@
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>999</v>
@@ -3289,7 +1776,7 @@
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>999</v>
@@ -3396,7 +1883,7 @@
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>999</v>
@@ -3503,7 +1990,7 @@
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>999</v>
@@ -3610,7 +2097,7 @@
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" s="6">
         <v>0</v>
@@ -3717,7 +2204,7 @@
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16" s="6">
         <v>0</v>
@@ -3824,7 +2311,7 @@
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17">
         <v>999</v>
@@ -3931,7 +2418,7 @@
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>999</v>
@@ -4038,7 +2525,7 @@
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>999</v>
@@ -4145,7 +2632,7 @@
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20">
         <v>999</v>
@@ -4252,7 +2739,7 @@
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>999</v>
@@ -4359,7 +2846,7 @@
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22">
         <v>999</v>

--- a/InputData/fuels/MPIiFE/Max Perc Inc in Fuel Exports.xlsx
+++ b/InputData/fuels/MPIiFE/Max Perc Inc in Fuel Exports.xlsx
@@ -1,31 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27421"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox (Energy Innovation)\EI-PlcyMdl\eps-1.5.0-us-wipM\InputData\fuels\MPIiFE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onewri-my.sharepoint.com/personal/shruti_dayal_wri_org/Documents/Desktop/Fuels updated files/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="36" documentId="11_BAE6435658E4090588FFFCC1881613E063D12F96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B3015BE-67B3-4BEA-8FBF-69ACD53EB78A}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28185" windowHeight="12510"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="MPIiFE" sheetId="2" r:id="rId2"/>
+    <sheet name="India trends" sheetId="3" r:id="rId2"/>
+    <sheet name="MPIiFE" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="100">
   <si>
     <t>MPIiFE Maximum Percentage Increase in Fuel Exports</t>
   </si>
@@ -33,78 +46,21 @@
     <t>Source:</t>
   </si>
   <si>
-    <t>none needed for U.S.</t>
+    <t>Ministry of Statistics and Programme Implementation</t>
+  </si>
+  <si>
+    <t>Energy Statistics 2023</t>
+  </si>
+  <si>
+    <t>https://www.mospi.gov.in/publication/energy-statistics-india-2023</t>
+  </si>
+  <si>
+    <t>Table 4.1; Page 42</t>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>electricity (not used in this variable)</t>
-  </si>
-  <si>
-    <t>hard coal</t>
-  </si>
-  <si>
-    <t>natural gas</t>
-  </si>
-  <si>
-    <t>nuclear</t>
-  </si>
-  <si>
-    <t>hydro (is not a fuel)</t>
-  </si>
-  <si>
-    <t>wind (is not a fuel)</t>
-  </si>
-  <si>
-    <t>solar (is not a fuel)</t>
-  </si>
-  <si>
-    <t>biomass</t>
-  </si>
-  <si>
-    <t>petroleum gasoline</t>
-  </si>
-  <si>
-    <t>petroleum diesel</t>
-  </si>
-  <si>
-    <t>biofuel gasoline</t>
-  </si>
-  <si>
-    <t>biofuel diesel</t>
-  </si>
-  <si>
-    <t>jet fuel or kerosene</t>
-  </si>
-  <si>
-    <t>heat (not used in this variable)</t>
-  </si>
-  <si>
-    <t>geothermal (is not a fuel)</t>
-  </si>
-  <si>
-    <t>lignite</t>
-  </si>
-  <si>
-    <t>crude oil</t>
-  </si>
-  <si>
-    <t>heavy fuel oil</t>
-  </si>
-  <si>
-    <t>LPG propane or butane</t>
-  </si>
-  <si>
-    <t>municipal solid waste</t>
-  </si>
-  <si>
-    <t>hydrogen</t>
-  </si>
-  <si>
-    <t>Max Percentage Increase (dimensionless)</t>
-  </si>
-  <si>
     <t>This variable allows you to specify a cap on how much fuel exports</t>
   </si>
   <si>
@@ -115,6 +71,9 @@
   </si>
   <si>
     <t>export terminal or trans-border pipeline capacity.</t>
+  </si>
+  <si>
+    <t>Alternatively, it may represent a legislative cap on exports.</t>
   </si>
   <si>
     <t>Note that even if this cap is high, fuel exports will not increase</t>
@@ -158,14 +117,262 @@
     <t>an arbitrarily high percentage.</t>
   </si>
   <si>
-    <t>Alternatively, it may represent a legislative cap on exports.</t>
+    <t>For India, in the historic trends from 2011-12 to 2021-22,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">there is a net positive CAGR in exports for petroleum products </t>
+  </si>
+  <si>
+    <t xml:space="preserve">and electricity. In case of petroleum products, this is because </t>
+  </si>
+  <si>
+    <t xml:space="preserve">of value addition to imported crude oil. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the case of coal, there is a net negative CAGR in the same </t>
+  </si>
+  <si>
+    <t>period. Coal supplies for thermal power plants have been a cause for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">concern in the recent years, with decline in plant performance due </t>
+  </si>
+  <si>
+    <t xml:space="preserve">to shortage of coal. Imports have been on rise, with not much increase in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">domestic coal production. Hence, it is not considered feasible for exports </t>
+  </si>
+  <si>
+    <t>to grow significantly in the sector. There are no natural gas and crude oil exports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">due to domestic shortages. MoPnG has communicated  </t>
+  </si>
+  <si>
+    <t>the presence of a roadmap to reduce oil import dependence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Various policy announcements to reduce fuel import dependence and </t>
+  </si>
+  <si>
+    <t xml:space="preserve">boost domestic production (e.g. Make in India), along with exemption of </t>
+  </si>
+  <si>
+    <t xml:space="preserve">taxes on export of fuels imply a focus towards increasing exports in the </t>
+  </si>
+  <si>
+    <t xml:space="preserve">medium to long-term. Based on recent trends, growth in exports is still </t>
+  </si>
+  <si>
+    <t xml:space="preserve">building slowly in the sectors with a net positive CAGR in the past decade. </t>
+  </si>
+  <si>
+    <t>Hence, it is not relevant/necessary to impose a cap on fuel exports</t>
+  </si>
+  <si>
+    <t>in India and we pick an arbitrarily high percentage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 4.1: Yearwise Foreign Trade in Coal, Crude Oil,  Petroleum Products(total), Natural Gas and Electricity </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                            (Million Tonnes)</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Coal</t>
+  </si>
+  <si>
+    <t>Lignite</t>
+  </si>
+  <si>
+    <t>Crude Oil</t>
+  </si>
+  <si>
+    <t>Petroleum Products</t>
+  </si>
+  <si>
+    <t>Gross</t>
+  </si>
+  <si>
+    <t>Exports</t>
+  </si>
+  <si>
+    <t>Net</t>
+  </si>
+  <si>
+    <t>Imports</t>
+  </si>
+  <si>
+    <t>4=(2)-(3)</t>
+  </si>
+  <si>
+    <t>7=(5)-(6)</t>
+  </si>
+  <si>
+    <t>10=(8)-(9)</t>
+  </si>
+  <si>
+    <t>13=(11)-(12)</t>
+  </si>
+  <si>
+    <t>2011-12</t>
+  </si>
+  <si>
+    <t>2012-13</t>
+  </si>
+  <si>
+    <t>2013-14</t>
+  </si>
+  <si>
+    <t>2014-15</t>
+  </si>
+  <si>
+    <t>2015-16</t>
+  </si>
+  <si>
+    <t>2016-17</t>
+  </si>
+  <si>
+    <t>2017-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-19 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-20 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-21 </t>
+  </si>
+  <si>
+    <t>2021-22 (P)</t>
+  </si>
+  <si>
+    <t>Growth rate of 2021-22 over 2020-21(%)</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CAGR 2012-13 to 2021-22   (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 4.1 (Contd): Yearwise Foreign Trade in Coal, Crude Oil,  Petroleum Products, Natural Gas and Electricity 
+</t>
+  </si>
+  <si>
+    <t>Natural Gas (BCM)</t>
+  </si>
+  <si>
+    <t>Electricity(Gwh)</t>
+  </si>
+  <si>
+    <t>Gross Imports</t>
+  </si>
+  <si>
+    <t>Net Imports</t>
+  </si>
+  <si>
+    <t>2020-21</t>
+  </si>
+  <si>
+    <t>(P): Provisional.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.  Office of Coal Controller, Ministry of Coal, </t>
+  </si>
+  <si>
+    <t>2.  Ministry of Petroleum &amp; Natural Gas.</t>
+  </si>
+  <si>
+    <t>3.  Central Electricity Authority</t>
+  </si>
+  <si>
+    <t>Source: Energy Statistics 2023</t>
+  </si>
+  <si>
+    <t>Max Percentage Increase (dimensionless)</t>
+  </si>
+  <si>
+    <t>electricity (not used in this variable)</t>
+  </si>
+  <si>
+    <t>hard coal</t>
+  </si>
+  <si>
+    <t>natural gas</t>
+  </si>
+  <si>
+    <t>nuclear</t>
+  </si>
+  <si>
+    <t>hydro (is not a fuel)</t>
+  </si>
+  <si>
+    <t>wind (is not a fuel)</t>
+  </si>
+  <si>
+    <t>solar (is not a fuel)</t>
+  </si>
+  <si>
+    <t>biomass</t>
+  </si>
+  <si>
+    <t>petroleum gasoline</t>
+  </si>
+  <si>
+    <t>petroleum diesel</t>
+  </si>
+  <si>
+    <t>biofuel gasoline</t>
+  </si>
+  <si>
+    <t>biofuel diesel</t>
+  </si>
+  <si>
+    <t>jet fuel or kerosene</t>
+  </si>
+  <si>
+    <t>heat (not used in this variable)</t>
+  </si>
+  <si>
+    <t>geothermal (is not a fuel)</t>
+  </si>
+  <si>
+    <t>lignite</t>
+  </si>
+  <si>
+    <t>crude oil</t>
+  </si>
+  <si>
+    <t>heavy fuel oil</t>
+  </si>
+  <si>
+    <t>LPG propane or butane</t>
+  </si>
+  <si>
+    <t>municipal solid waste</t>
+  </si>
+  <si>
+    <t>hydrogen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -181,8 +388,97 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -195,8 +491,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -204,28 +524,398 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -503,81 +1193,201 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="55" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="B4" s="56">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -587,233 +1397,1625 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C8D42D0-4141-4ABB-998E-87F3C4B0CD72}">
+  <dimension ref="A2:N49"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14" ht="15">
+      <c r="B2" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="69"/>
+    </row>
+    <row r="3" spans="2:14">
+      <c r="B3" s="70" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="72"/>
+    </row>
+    <row r="4" spans="2:14">
+      <c r="B4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="73" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="74"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="74"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="76" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="77"/>
+      <c r="K4" s="78"/>
+      <c r="L4" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="M4" s="77"/>
+      <c r="N4" s="78"/>
+    </row>
+    <row r="5" spans="2:14">
+      <c r="B5" s="9"/>
+      <c r="C5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="13"/>
+      <c r="E6" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="13"/>
+      <c r="H6" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="13"/>
+      <c r="N6" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14">
+      <c r="B7" s="18">
+        <v>1</v>
+      </c>
+      <c r="C7" s="18">
+        <v>2</v>
+      </c>
+      <c r="D7" s="19">
+        <v>3</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="19">
+        <v>5</v>
+      </c>
+      <c r="G7" s="19">
+        <v>6</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" s="20">
+        <v>8</v>
+      </c>
+      <c r="J7" s="20">
+        <v>9</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" s="20">
+        <v>11</v>
+      </c>
+      <c r="M7" s="20">
+        <v>12</v>
+      </c>
+      <c r="N7" s="22" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14">
+      <c r="B8" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="23">
+        <v>102.85262600000003</v>
+      </c>
+      <c r="D8" s="23">
+        <v>2.0146999999999995</v>
+      </c>
+      <c r="E8" s="23">
+        <f>C8-D8</f>
+        <v>100.83792600000002</v>
+      </c>
+      <c r="F8" s="23">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="G8" s="23">
+        <v>0</v>
+      </c>
+      <c r="H8" s="23">
+        <f>F8-G8</f>
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="I8" s="23">
+        <v>171.729154097221</v>
+      </c>
+      <c r="J8" s="23">
+        <v>0</v>
+      </c>
+      <c r="K8" s="23">
+        <f t="shared" ref="K8:K18" si="0">I8-J8</f>
+        <v>171.729154097221</v>
+      </c>
+      <c r="L8" s="23">
+        <v>15.849370446253001</v>
+      </c>
+      <c r="M8" s="23">
+        <v>60.837340519999998</v>
+      </c>
+      <c r="N8" s="23">
+        <f t="shared" ref="N8:N18" si="1">L8-M8</f>
+        <v>-44.987970073746993</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14">
+      <c r="B9" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="24">
+        <v>145.78544500000001</v>
+      </c>
+      <c r="D9" s="24">
+        <v>2.4429620000000001</v>
+      </c>
+      <c r="E9" s="24">
+        <f t="shared" ref="E9:E18" si="2">C9-D9</f>
+        <v>143.34248300000002</v>
+      </c>
+      <c r="F9" s="24">
+        <v>5.5000000000000003E-4</v>
+      </c>
+      <c r="G9" s="24">
+        <v>6.9059999999999996E-2</v>
+      </c>
+      <c r="H9" s="24">
+        <f t="shared" ref="H9:H18" si="3">F9-G9</f>
+        <v>-6.8510000000000001E-2</v>
+      </c>
+      <c r="I9" s="24">
+        <v>184.79524788937999</v>
+      </c>
+      <c r="J9" s="24">
+        <v>0</v>
+      </c>
+      <c r="K9" s="24">
+        <f t="shared" si="0"/>
+        <v>184.79524788937999</v>
+      </c>
+      <c r="L9" s="24">
+        <v>16.354119653000001</v>
+      </c>
+      <c r="M9" s="24">
+        <v>63.407761975930008</v>
+      </c>
+      <c r="N9" s="24">
+        <f t="shared" si="1"/>
+        <v>-47.053642322930003</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14">
+      <c r="B10" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="24">
+        <v>166.85702300000003</v>
+      </c>
+      <c r="D10" s="24">
+        <v>2.1880830000000002</v>
+      </c>
+      <c r="E10" s="24">
+        <f t="shared" si="2"/>
+        <v>164.66894000000002</v>
+      </c>
+      <c r="F10" s="24">
+        <v>1.2700000000000001E-3</v>
+      </c>
+      <c r="G10" s="24">
+        <v>1.9400000000000001E-3</v>
+      </c>
+      <c r="H10" s="24">
+        <f t="shared" si="3"/>
+        <v>-6.7000000000000002E-4</v>
+      </c>
+      <c r="I10" s="24">
+        <v>189.23820178337502</v>
+      </c>
+      <c r="J10" s="24">
+        <v>0</v>
+      </c>
+      <c r="K10" s="24">
+        <f t="shared" si="0"/>
+        <v>189.23820178337502</v>
+      </c>
+      <c r="L10" s="24">
+        <v>16.697004688</v>
+      </c>
+      <c r="M10" s="24">
+        <v>67.864014699800009</v>
+      </c>
+      <c r="N10" s="24">
+        <f t="shared" si="1"/>
+        <v>-51.167010011800009</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14">
+      <c r="B11" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="24">
+        <v>217.78279499999999</v>
+      </c>
+      <c r="D11" s="24">
+        <v>1.238375</v>
+      </c>
+      <c r="E11" s="24">
+        <f t="shared" si="2"/>
+        <v>216.54442</v>
+      </c>
+      <c r="F11" s="24">
+        <v>6.4000000000000005E-4</v>
+      </c>
+      <c r="G11" s="24">
+        <v>2.8500000000000001E-3</v>
+      </c>
+      <c r="H11" s="24">
+        <f t="shared" si="3"/>
+        <v>-2.2100000000000002E-3</v>
+      </c>
+      <c r="I11" s="24">
+        <v>189.43485654402394</v>
+      </c>
+      <c r="J11" s="24">
+        <v>0</v>
+      </c>
+      <c r="K11" s="24">
+        <f t="shared" si="0"/>
+        <v>189.43485654402394</v>
+      </c>
+      <c r="L11" s="24">
+        <v>21.301161557</v>
+      </c>
+      <c r="M11" s="24">
+        <v>63.931857026299994</v>
+      </c>
+      <c r="N11" s="24">
+        <f t="shared" si="1"/>
+        <v>-42.630695469299994</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14">
+      <c r="B12" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="24">
+        <v>203.94926100000001</v>
+      </c>
+      <c r="D12" s="24">
+        <v>1.575186</v>
+      </c>
+      <c r="E12" s="24">
+        <f t="shared" si="2"/>
+        <v>202.374075</v>
+      </c>
+      <c r="F12" s="24">
+        <v>1.0499999999999999E-3</v>
+      </c>
+      <c r="G12" s="24">
+        <v>5.1000000000000004E-4</v>
+      </c>
+      <c r="H12" s="24">
+        <f t="shared" si="3"/>
+        <v>5.399999999999999E-4</v>
+      </c>
+      <c r="I12" s="24">
+        <v>202.85049173136341</v>
+      </c>
+      <c r="J12" s="24">
+        <v>0</v>
+      </c>
+      <c r="K12" s="24">
+        <f t="shared" si="0"/>
+        <v>202.85049173136341</v>
+      </c>
+      <c r="L12" s="24">
+        <v>29.455754196099996</v>
+      </c>
+      <c r="M12" s="24">
+        <v>60.538562213000006</v>
+      </c>
+      <c r="N12" s="24">
+        <f t="shared" si="1"/>
+        <v>-31.08280801690001</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14">
+      <c r="B13" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="24">
+        <v>190.95304599999997</v>
+      </c>
+      <c r="D13" s="24">
+        <v>1.7726470000000003</v>
+      </c>
+      <c r="E13" s="24">
+        <f t="shared" si="2"/>
+        <v>189.18039899999997</v>
+      </c>
+      <c r="F13" s="24">
+        <v>1.9120000000000002E-2</v>
+      </c>
+      <c r="G13" s="24">
+        <v>5.3800000000000002E-3</v>
+      </c>
+      <c r="H13" s="24">
+        <f t="shared" si="3"/>
+        <v>1.3740000000000002E-2</v>
+      </c>
+      <c r="I13" s="24">
+        <v>213.93202953023484</v>
+      </c>
+      <c r="J13" s="24">
+        <v>0</v>
+      </c>
+      <c r="K13" s="24">
+        <f t="shared" si="0"/>
+        <v>213.93202953023484</v>
+      </c>
+      <c r="L13" s="24">
+        <v>36.287331375000001</v>
+      </c>
+      <c r="M13" s="24">
+        <v>65.51346949068099</v>
+      </c>
+      <c r="N13" s="24">
+        <f t="shared" si="1"/>
+        <v>-29.226138115680989</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14">
+      <c r="B14" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="25">
+        <v>208.24867299999997</v>
+      </c>
+      <c r="D14" s="25">
+        <v>1.5036539999999996</v>
+      </c>
+      <c r="E14" s="25">
+        <f t="shared" si="2"/>
+        <v>206.74501899999996</v>
+      </c>
+      <c r="F14" s="25">
+        <v>1.0410000000000001E-2</v>
+      </c>
+      <c r="G14" s="25">
+        <v>4.4099999999999999E-3</v>
+      </c>
+      <c r="H14" s="25">
+        <f t="shared" si="3"/>
+        <v>6.000000000000001E-3</v>
+      </c>
+      <c r="I14" s="25">
+        <v>220.43279203083119</v>
+      </c>
+      <c r="J14" s="25">
+        <v>0</v>
+      </c>
+      <c r="K14" s="25">
+        <f t="shared" si="0"/>
+        <v>220.43279203083119</v>
+      </c>
+      <c r="L14" s="25">
+        <v>35.460834880927038</v>
+      </c>
+      <c r="M14" s="25">
+        <v>66.832729412250004</v>
+      </c>
+      <c r="N14" s="25">
+        <f t="shared" si="1"/>
+        <v>-31.371894531322965</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14">
+      <c r="B15" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="27">
+        <v>235.34801299999992</v>
+      </c>
+      <c r="D15" s="27">
+        <v>1.3063739999999995</v>
+      </c>
+      <c r="E15" s="27">
+        <f t="shared" si="2"/>
+        <v>234.04163899999992</v>
+      </c>
+      <c r="F15" s="27">
+        <v>1.9369999999999998E-2</v>
+      </c>
+      <c r="G15" s="27">
+        <v>7.8939999999999996E-2</v>
+      </c>
+      <c r="H15" s="27">
+        <f t="shared" si="3"/>
+        <v>-5.9569999999999998E-2</v>
+      </c>
+      <c r="I15" s="27">
+        <v>226.49761635146419</v>
+      </c>
+      <c r="J15" s="27">
+        <v>0</v>
+      </c>
+      <c r="K15" s="27">
+        <f t="shared" si="0"/>
+        <v>226.49761635146419</v>
+      </c>
+      <c r="L15" s="27">
+        <v>33.348324303199995</v>
+      </c>
+      <c r="M15" s="27">
+        <v>61.095732773732657</v>
+      </c>
+      <c r="N15" s="27">
+        <f t="shared" si="1"/>
+        <v>-27.747408470532662</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14">
+      <c r="B16" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="27">
+        <v>248.53658099999998</v>
+      </c>
+      <c r="D16" s="27">
+        <v>1.0297700000000001</v>
+      </c>
+      <c r="E16" s="27">
+        <f t="shared" si="2"/>
+        <v>247.50681099999997</v>
+      </c>
+      <c r="F16" s="27">
+        <v>5.425E-2</v>
+      </c>
+      <c r="G16" s="27">
+        <v>9.2660000000000006E-2</v>
+      </c>
+      <c r="H16" s="27">
+        <f t="shared" si="3"/>
+        <v>-3.8410000000000007E-2</v>
+      </c>
+      <c r="I16" s="27">
+        <v>226.95466551568416</v>
+      </c>
+      <c r="J16" s="27">
+        <v>0</v>
+      </c>
+      <c r="K16" s="27">
+        <f t="shared" si="0"/>
+        <v>226.95466551568416</v>
+      </c>
+      <c r="L16" s="27">
+        <v>43.787610787399998</v>
+      </c>
+      <c r="M16" s="27">
+        <v>65.685236175397193</v>
+      </c>
+      <c r="N16" s="27">
+        <f t="shared" si="1"/>
+        <v>-21.897625387997195</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="27">
+        <v>215.25111500000006</v>
+      </c>
+      <c r="D17" s="27">
+        <v>2.9451880000000008</v>
+      </c>
+      <c r="E17" s="27">
+        <f t="shared" si="2"/>
+        <v>212.30592700000005</v>
+      </c>
+      <c r="F17" s="27">
+        <v>1.8859999999999998E-2</v>
+      </c>
+      <c r="G17" s="27">
+        <v>0.18739</v>
+      </c>
+      <c r="H17" s="27">
+        <f t="shared" si="3"/>
+        <v>-0.16853000000000001</v>
+      </c>
+      <c r="I17" s="27">
+        <v>196.46086094549045</v>
+      </c>
+      <c r="J17" s="27">
+        <v>0</v>
+      </c>
+      <c r="K17" s="27">
+        <f t="shared" si="0"/>
+        <v>196.46086094549045</v>
+      </c>
+      <c r="L17" s="27">
+        <v>43.247663142000007</v>
+      </c>
+      <c r="M17" s="27">
+        <v>56.768700356004253</v>
+      </c>
+      <c r="N17" s="27">
+        <f t="shared" si="1"/>
+        <v>-13.521037214004245</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="27">
+        <v>208.934</v>
+      </c>
+      <c r="D18" s="27">
+        <v>1.169</v>
+      </c>
+      <c r="E18" s="27">
+        <f t="shared" si="2"/>
+        <v>207.76499999999999</v>
+      </c>
+      <c r="F18" s="27">
+        <v>6.7699999999999996E-2</v>
+      </c>
+      <c r="G18" s="27">
+        <v>1.7600000000000001E-2</v>
+      </c>
+      <c r="H18" s="27">
+        <f t="shared" si="3"/>
+        <v>5.0099999999999992E-2</v>
+      </c>
+      <c r="I18" s="27">
+        <v>211.97987243623956</v>
+      </c>
+      <c r="J18" s="27">
+        <v>0</v>
+      </c>
+      <c r="K18" s="27">
+        <f t="shared" si="0"/>
+        <v>211.97987243623956</v>
+      </c>
+      <c r="L18" s="27">
+        <v>42.061691697999997</v>
+      </c>
+      <c r="M18" s="27">
+        <v>62.712741283085158</v>
+      </c>
+      <c r="N18" s="27">
+        <f t="shared" si="1"/>
+        <v>-20.651049585085161</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" ht="51.95">
+      <c r="B19" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="29">
+        <f>+(C18-C17)/C17*100</f>
+        <v>-2.9347652856525537</v>
+      </c>
+      <c r="D19" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="29">
+        <f t="shared" ref="E19:I19" si="4">+(E18-E17)/E17*100</f>
+        <v>-2.1388602118489453</v>
+      </c>
+      <c r="F19" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="G19" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="H19" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="I19" s="29">
+        <f t="shared" si="4"/>
+        <v>7.8992891592055958</v>
+      </c>
+      <c r="J19" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="K19" s="29">
+        <f t="shared" ref="K19:M19" si="5">+(K18-K17)/K17*100</f>
+        <v>7.8992891592055958</v>
+      </c>
+      <c r="L19" s="29">
+        <f t="shared" si="5"/>
+        <v>-2.7422786755112631</v>
+      </c>
+      <c r="M19" s="29">
+        <f t="shared" si="5"/>
+        <v>10.470630628858887</v>
+      </c>
+      <c r="N19" s="29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" ht="39">
+      <c r="B20" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="29">
+        <f>((C18/C9)^(1/9)-1)*100</f>
+        <v>4.0797177425300424</v>
+      </c>
+      <c r="D20" s="29">
+        <f t="shared" ref="D20:N20" si="6">((D18/D9)^(1/9)-1)*100</f>
+        <v>-7.863207610873002</v>
+      </c>
+      <c r="E20" s="29">
+        <f t="shared" si="6"/>
+        <v>4.2103439894769279</v>
+      </c>
+      <c r="F20" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20" s="29">
+        <f t="shared" si="6"/>
+        <v>-14.09236006681417</v>
+      </c>
+      <c r="H20" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="I20" s="29">
+        <f t="shared" si="6"/>
+        <v>1.5366071884427512</v>
+      </c>
+      <c r="J20" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="K20" s="29">
+        <f t="shared" si="6"/>
+        <v>1.5366071884427512</v>
+      </c>
+      <c r="L20" s="29">
+        <f t="shared" si="6"/>
+        <v>11.066834965535488</v>
+      </c>
+      <c r="M20" s="29">
+        <f t="shared" si="6"/>
+        <v>-0.12238777101329923</v>
+      </c>
+      <c r="N20" s="29">
+        <f t="shared" si="6"/>
+        <v>-8.7440927877327272</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" ht="15">
+      <c r="B21" s="30"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+      <c r="N21" s="31"/>
+    </row>
+    <row r="22" spans="2:14" ht="20.100000000000001">
+      <c r="B22" s="57" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="35"/>
+    </row>
+    <row r="23" spans="2:14" ht="20.100000000000001">
+      <c r="B23" s="60"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="35"/>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="64"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="66"/>
+      <c r="H24" s="65"/>
+      <c r="K24" s="32"/>
+      <c r="M24" s="34"/>
+      <c r="N24" s="32"/>
+    </row>
+    <row r="25" spans="2:14" ht="26.1">
+      <c r="B25" s="9"/>
+      <c r="C25" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="K25" s="32"/>
+      <c r="N25" s="32"/>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26" s="18">
+        <v>1</v>
+      </c>
+      <c r="C26" s="39">
+        <v>11</v>
+      </c>
+      <c r="D26" s="39">
+        <v>12</v>
+      </c>
+      <c r="E26" s="39">
+        <v>13</v>
+      </c>
+      <c r="F26" s="39">
+        <v>14</v>
+      </c>
+      <c r="G26" s="39">
+        <v>15</v>
+      </c>
+      <c r="H26" s="39">
+        <v>16</v>
+      </c>
+      <c r="K26" s="32"/>
+      <c r="N26" s="32"/>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="23">
+        <v>17.997333624870201</v>
+      </c>
+      <c r="D27" s="23">
+        <v>0</v>
+      </c>
+      <c r="E27" s="23">
+        <f>C27-D27</f>
+        <v>17.997333624870201</v>
+      </c>
+      <c r="F27" s="23">
+        <v>5252.7</v>
+      </c>
+      <c r="G27" s="23">
+        <v>134.75</v>
+      </c>
+      <c r="H27" s="23">
+        <f>F27-G27</f>
+        <v>5117.95</v>
+      </c>
+      <c r="K27" s="32"/>
+      <c r="N27" s="32"/>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="24">
+        <v>17.614399539818521</v>
+      </c>
+      <c r="D28" s="24">
+        <v>0</v>
+      </c>
+      <c r="E28" s="24">
+        <f>C28-D28</f>
+        <v>17.614399539818521</v>
+      </c>
+      <c r="F28" s="24">
+        <v>4794.5</v>
+      </c>
+      <c r="G28" s="24">
+        <v>153.53</v>
+      </c>
+      <c r="H28" s="24">
+        <f t="shared" ref="H28:H37" si="7">F28-G28</f>
+        <v>4640.97</v>
+      </c>
+      <c r="K28" s="32"/>
+      <c r="N28" s="32"/>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="24">
+        <v>17.800797802276925</v>
+      </c>
+      <c r="D29" s="24">
+        <v>0</v>
+      </c>
+      <c r="E29" s="24">
+        <f t="shared" ref="E29:E37" si="8">C29-D29</f>
+        <v>17.800797802276925</v>
+      </c>
+      <c r="F29" s="24">
+        <v>5597.9</v>
+      </c>
+      <c r="G29" s="24">
+        <v>1651</v>
+      </c>
+      <c r="H29" s="24">
+        <f t="shared" si="7"/>
+        <v>3946.8999999999996</v>
+      </c>
+      <c r="K29" s="32"/>
+      <c r="N29" s="32"/>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="24">
+        <v>18.606529815330337</v>
+      </c>
+      <c r="D30" s="24">
+        <v>0</v>
+      </c>
+      <c r="E30" s="24">
+        <f t="shared" si="8"/>
+        <v>18.606529815330337</v>
+      </c>
+      <c r="F30" s="24">
+        <v>5007.74</v>
+      </c>
+      <c r="G30" s="24">
+        <v>4432.7602800000004</v>
+      </c>
+      <c r="H30" s="24">
+        <f t="shared" si="7"/>
+        <v>574.97971999999936</v>
+      </c>
+      <c r="K30" s="32"/>
+      <c r="N30" s="32"/>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="24">
+        <v>21.388273157442317</v>
+      </c>
+      <c r="D31" s="24">
+        <v>0</v>
+      </c>
+      <c r="E31" s="24">
+        <f t="shared" si="8"/>
+        <v>21.388273157442317</v>
+      </c>
+      <c r="F31" s="24">
+        <v>5244.21</v>
+      </c>
+      <c r="G31" s="24">
+        <v>5150.3000452999995</v>
+      </c>
+      <c r="H31" s="24">
+        <f t="shared" si="7"/>
+        <v>93.909954700000526</v>
+      </c>
+      <c r="K31" s="32"/>
+      <c r="N31" s="32"/>
+    </row>
+    <row r="32" spans="2:14">
+      <c r="B32" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="24">
+        <v>24.848992618968182</v>
+      </c>
+      <c r="D32" s="24">
+        <v>0</v>
+      </c>
+      <c r="E32" s="24">
+        <f t="shared" si="8"/>
+        <v>24.848992618968182</v>
+      </c>
+      <c r="F32" s="24">
+        <v>5617.3</v>
+      </c>
+      <c r="G32" s="24">
+        <v>6710.1867269999993</v>
+      </c>
+      <c r="H32" s="24">
+        <f t="shared" si="7"/>
+        <v>-1092.8867269999992</v>
+      </c>
+      <c r="K32" s="32"/>
+      <c r="N32" s="32"/>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="B33" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="25">
+        <v>27.438951466006877</v>
+      </c>
+      <c r="D33" s="25">
+        <v>0</v>
+      </c>
+      <c r="E33" s="25">
+        <f t="shared" si="8"/>
+        <v>27.438951466006877</v>
+      </c>
+      <c r="F33" s="25">
+        <v>5072.08</v>
+      </c>
+      <c r="G33" s="25">
+        <v>7202.86</v>
+      </c>
+      <c r="H33" s="25">
+        <f t="shared" si="7"/>
+        <v>-2130.7799999999997</v>
+      </c>
+      <c r="K33" s="32"/>
+      <c r="N33" s="32"/>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="B34" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="27">
+        <v>28.740457768307444</v>
+      </c>
+      <c r="D34" s="27">
+        <v>0</v>
+      </c>
+      <c r="E34" s="27">
+        <f t="shared" si="8"/>
+        <v>28.740457768307444</v>
+      </c>
+      <c r="F34" s="27">
+        <v>4395.8599999999997</v>
+      </c>
+      <c r="G34" s="27">
+        <v>8468.9389699999992</v>
+      </c>
+      <c r="H34" s="27">
+        <f t="shared" si="7"/>
+        <v>-4073.0789699999996</v>
+      </c>
+      <c r="K34" s="32"/>
+      <c r="N34" s="32"/>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="B35" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="27">
+        <v>33.886686048486638</v>
+      </c>
+      <c r="D35" s="27">
+        <v>0</v>
+      </c>
+      <c r="E35" s="27">
+        <f t="shared" si="8"/>
+        <v>33.886686048486638</v>
+      </c>
+      <c r="F35" s="27">
+        <v>6350.6</v>
+      </c>
+      <c r="G35" s="27">
+        <v>9490.91</v>
+      </c>
+      <c r="H35" s="27">
+        <f t="shared" si="7"/>
+        <v>-3140.3099999999995</v>
+      </c>
+      <c r="K35" s="32"/>
+      <c r="N35" s="32"/>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="B36" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="27">
+        <v>33.031366325346504</v>
+      </c>
+      <c r="D36" s="27">
+        <v>0</v>
+      </c>
+      <c r="E36" s="27">
+        <f t="shared" si="8"/>
+        <v>33.031366325346504</v>
+      </c>
+      <c r="F36" s="27">
+        <v>9547.7000000000007</v>
+      </c>
+      <c r="G36" s="27">
+        <v>9573.5519540000005</v>
+      </c>
+      <c r="H36" s="27">
+        <f t="shared" si="7"/>
+        <v>-25.851953999999751</v>
+      </c>
+      <c r="K36" s="32"/>
+      <c r="L36" s="40"/>
+      <c r="N36" s="32"/>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="B37" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="27">
+        <v>30.776102336565117</v>
+      </c>
+      <c r="D37" s="27">
+        <v>0</v>
+      </c>
+      <c r="E37" s="27">
+        <f t="shared" si="8"/>
+        <v>30.776102336565117</v>
+      </c>
+      <c r="F37" s="27">
+        <v>7596.71</v>
+      </c>
+      <c r="G37" s="27">
+        <v>9231.6299999999992</v>
+      </c>
+      <c r="H37" s="27">
+        <f t="shared" si="7"/>
+        <v>-1634.9199999999992</v>
+      </c>
+      <c r="K37" s="32"/>
+    </row>
+    <row r="38" spans="1:14" ht="65.099999999999994">
+      <c r="B38" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="29">
+        <f t="shared" ref="C38:G38" si="9">+(C37-C36)/C36*100</f>
+        <v>-6.8276436601740498</v>
+      </c>
+      <c r="D38" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" s="29">
+        <f t="shared" si="9"/>
+        <v>-6.8276436601740498</v>
+      </c>
+      <c r="F38" s="29">
+        <f t="shared" si="9"/>
+        <v>-20.434135969919463</v>
+      </c>
+      <c r="G38" s="29">
+        <f t="shared" si="9"/>
+        <v>-3.5715265937125893</v>
+      </c>
+      <c r="H38" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="K38" s="32"/>
+      <c r="N38" s="32"/>
+    </row>
+    <row r="39" spans="1:14" ht="51.95">
+      <c r="B39" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" s="41">
+        <f>((C37/C28)^(1/9)-1)*100</f>
+        <v>6.3964918035506857</v>
+      </c>
+      <c r="D39" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="E39" s="41">
+        <f t="shared" ref="E39:G39" si="10">((E37/E28)^(1/9)-1)*100</f>
+        <v>6.3964918035506857</v>
+      </c>
+      <c r="F39" s="41">
+        <f t="shared" si="10"/>
+        <v>5.2468571889327631</v>
+      </c>
+      <c r="G39" s="41">
+        <f t="shared" si="10"/>
+        <v>57.643521108011718</v>
+      </c>
+      <c r="H39" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="K39" s="32"/>
+      <c r="N39" s="32"/>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="B40" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="C40" s="43"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="46"/>
+      <c r="N40" s="32"/>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="B41" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="45"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="45"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="46"/>
+      <c r="N41" s="32"/>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="B42" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="C42" s="45"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="49"/>
+      <c r="N42" s="32"/>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="B43" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="C43" s="50"/>
+      <c r="D43" s="50"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="49"/>
+      <c r="N43" s="32"/>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="B44" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="52"/>
+      <c r="H44" s="53"/>
+      <c r="N44" s="32"/>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="15">
+      <c r="A48" s="79" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B22:H23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="L4:N4"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A48" r:id="rId1" xr:uid="{8E5EACB5-85BA-4E8F-BAC4-8CF280EF8D59}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AI22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BC22"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:55">
       <c r="A1" s="2" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="B1" s="3">
         <v>2017</v>
       </c>
-      <c r="C1" s="4">
+      <c r="C1">
         <v>2018</v>
       </c>
       <c r="D1" s="3">
         <v>2019</v>
       </c>
-      <c r="E1" s="4">
+      <c r="E1">
         <v>2020</v>
       </c>
       <c r="F1" s="3">
         <v>2021</v>
       </c>
-      <c r="G1" s="4">
+      <c r="G1">
         <v>2022</v>
       </c>
       <c r="H1" s="3">
         <v>2023</v>
       </c>
-      <c r="I1" s="4">
+      <c r="I1">
         <v>2024</v>
       </c>
       <c r="J1" s="3">
         <v>2025</v>
       </c>
-      <c r="K1" s="4">
+      <c r="K1">
         <v>2026</v>
       </c>
       <c r="L1" s="3">
         <v>2027</v>
       </c>
-      <c r="M1" s="4">
+      <c r="M1">
         <v>2028</v>
       </c>
       <c r="N1" s="3">
         <v>2029</v>
       </c>
-      <c r="O1" s="4">
+      <c r="O1">
         <v>2030</v>
       </c>
       <c r="P1" s="3">
         <v>2031</v>
       </c>
-      <c r="Q1" s="4">
+      <c r="Q1">
         <v>2032</v>
       </c>
       <c r="R1" s="3">
         <v>2033</v>
       </c>
-      <c r="S1" s="4">
+      <c r="S1">
         <v>2034</v>
       </c>
       <c r="T1" s="3">
         <v>2035</v>
       </c>
-      <c r="U1" s="4">
+      <c r="U1">
         <v>2036</v>
       </c>
       <c r="V1" s="3">
         <v>2037</v>
       </c>
-      <c r="W1" s="4">
+      <c r="W1">
         <v>2038</v>
       </c>
       <c r="X1" s="3">
         <v>2039</v>
       </c>
-      <c r="Y1" s="4">
+      <c r="Y1">
         <v>2040</v>
       </c>
       <c r="Z1" s="3">
         <v>2041</v>
       </c>
-      <c r="AA1" s="4">
+      <c r="AA1">
         <v>2042</v>
       </c>
       <c r="AB1" s="3">
         <v>2043</v>
       </c>
-      <c r="AC1" s="4">
+      <c r="AC1">
         <v>2044</v>
       </c>
       <c r="AD1" s="3">
         <v>2045</v>
       </c>
-      <c r="AE1" s="4">
+      <c r="AE1">
         <v>2046</v>
       </c>
       <c r="AF1" s="3">
         <v>2047</v>
       </c>
-      <c r="AG1" s="4">
+      <c r="AG1">
         <v>2048</v>
       </c>
       <c r="AH1" s="3">
         <v>2049</v>
       </c>
-      <c r="AI1" s="4">
+      <c r="AI1">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="6">
-        <v>0</v>
-      </c>
-      <c r="C2" s="6">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6">
-        <v>0</v>
-      </c>
-      <c r="E2" s="6">
-        <v>0</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0</v>
-      </c>
-      <c r="G2" s="6">
-        <v>0</v>
-      </c>
-      <c r="H2" s="6">
-        <v>0</v>
-      </c>
-      <c r="I2" s="6">
-        <v>0</v>
-      </c>
-      <c r="J2" s="6">
-        <v>0</v>
-      </c>
-      <c r="K2" s="6">
-        <v>0</v>
-      </c>
-      <c r="L2" s="6">
-        <v>0</v>
-      </c>
-      <c r="M2" s="6">
-        <v>0</v>
-      </c>
-      <c r="N2" s="6">
-        <v>0</v>
-      </c>
-      <c r="O2" s="6">
-        <v>0</v>
-      </c>
-      <c r="P2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="6">
-        <v>0</v>
-      </c>
-      <c r="R2" s="6">
-        <v>0</v>
-      </c>
-      <c r="S2" s="6">
-        <v>0</v>
-      </c>
-      <c r="T2" s="6">
-        <v>0</v>
-      </c>
-      <c r="U2" s="6">
-        <v>0</v>
-      </c>
-      <c r="V2" s="6">
-        <v>0</v>
-      </c>
-      <c r="W2" s="6">
-        <v>0</v>
-      </c>
-      <c r="X2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>5</v>
+      <c r="AJ1" s="3">
+        <v>2051</v>
+      </c>
+      <c r="AK1" s="3">
+        <v>2052</v>
+      </c>
+      <c r="AL1" s="3">
+        <v>2053</v>
+      </c>
+      <c r="AM1" s="3">
+        <v>2054</v>
+      </c>
+      <c r="AN1" s="3">
+        <v>2055</v>
+      </c>
+      <c r="AO1" s="3">
+        <v>2056</v>
+      </c>
+      <c r="AP1" s="3">
+        <v>2057</v>
+      </c>
+      <c r="AQ1" s="3">
+        <v>2058</v>
+      </c>
+      <c r="AR1" s="3">
+        <v>2059</v>
+      </c>
+      <c r="AS1" s="3">
+        <v>2060</v>
+      </c>
+      <c r="AT1" s="3">
+        <v>2061</v>
+      </c>
+      <c r="AU1" s="3">
+        <v>2062</v>
+      </c>
+      <c r="AV1" s="3">
+        <v>2063</v>
+      </c>
+      <c r="AW1" s="3">
+        <v>2064</v>
+      </c>
+      <c r="AX1" s="3">
+        <v>2065</v>
+      </c>
+      <c r="AY1" s="3">
+        <v>2066</v>
+      </c>
+      <c r="AZ1" s="3">
+        <v>2067</v>
+      </c>
+      <c r="BA1" s="3">
+        <v>2068</v>
+      </c>
+      <c r="BB1" s="3">
+        <v>2069</v>
+      </c>
+      <c r="BC1" s="3">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:55">
+      <c r="A2" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0</v>
+      </c>
+      <c r="R2" s="4">
+        <v>0</v>
+      </c>
+      <c r="S2" s="4">
+        <v>0</v>
+      </c>
+      <c r="T2" s="4">
+        <v>0</v>
+      </c>
+      <c r="U2" s="4">
+        <v>0</v>
+      </c>
+      <c r="V2" s="4">
+        <v>0</v>
+      </c>
+      <c r="W2" s="4">
+        <v>0</v>
+      </c>
+      <c r="X2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:55">
+      <c r="A3" t="s">
+        <v>80</v>
       </c>
       <c r="B3">
         <v>999</v>
@@ -918,9 +3120,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>6</v>
+    <row r="4" spans="1:55">
+      <c r="A4" t="s">
+        <v>81</v>
       </c>
       <c r="B4">
         <v>999</v>
@@ -1025,9 +3227,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>7</v>
+    <row r="5" spans="1:55">
+      <c r="A5" t="s">
+        <v>82</v>
       </c>
       <c r="B5">
         <v>999</v>
@@ -1132,330 +3334,330 @@
         <v>999</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="6">
-        <v>0</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0</v>
-      </c>
-      <c r="D6" s="6">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6">
-        <v>0</v>
-      </c>
-      <c r="J6" s="6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="6">
-        <v>0</v>
-      </c>
-      <c r="M6" s="6">
-        <v>0</v>
-      </c>
-      <c r="N6" s="6">
-        <v>0</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>0</v>
-      </c>
-      <c r="R6" s="6">
-        <v>0</v>
-      </c>
-      <c r="S6" s="6">
-        <v>0</v>
-      </c>
-      <c r="T6" s="6">
-        <v>0</v>
-      </c>
-      <c r="U6" s="6">
-        <v>0</v>
-      </c>
-      <c r="V6" s="6">
-        <v>0</v>
-      </c>
-      <c r="W6" s="6">
-        <v>0</v>
-      </c>
-      <c r="X6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6">
-        <v>0</v>
-      </c>
-      <c r="K7" s="6">
-        <v>0</v>
-      </c>
-      <c r="L7" s="6">
-        <v>0</v>
-      </c>
-      <c r="M7" s="6">
-        <v>0</v>
-      </c>
-      <c r="N7" s="6">
-        <v>0</v>
-      </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>0</v>
-      </c>
-      <c r="R7" s="6">
-        <v>0</v>
-      </c>
-      <c r="S7" s="6">
-        <v>0</v>
-      </c>
-      <c r="T7" s="6">
-        <v>0</v>
-      </c>
-      <c r="U7" s="6">
-        <v>0</v>
-      </c>
-      <c r="V7" s="6">
-        <v>0</v>
-      </c>
-      <c r="W7" s="6">
-        <v>0</v>
-      </c>
-      <c r="X7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="6">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6">
-        <v>0</v>
-      </c>
-      <c r="K8" s="6">
-        <v>0</v>
-      </c>
-      <c r="L8" s="6">
-        <v>0</v>
-      </c>
-      <c r="M8" s="6">
-        <v>0</v>
-      </c>
-      <c r="N8" s="6">
-        <v>0</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>0</v>
-      </c>
-      <c r="R8" s="6">
-        <v>0</v>
-      </c>
-      <c r="S8" s="6">
-        <v>0</v>
-      </c>
-      <c r="T8" s="6">
-        <v>0</v>
-      </c>
-      <c r="U8" s="6">
-        <v>0</v>
-      </c>
-      <c r="V8" s="6">
-        <v>0</v>
-      </c>
-      <c r="W8" s="6">
-        <v>0</v>
-      </c>
-      <c r="X8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>11</v>
+    <row r="6" spans="1:55">
+      <c r="A6" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4">
+        <v>0</v>
+      </c>
+      <c r="S6" s="4">
+        <v>0</v>
+      </c>
+      <c r="T6" s="4">
+        <v>0</v>
+      </c>
+      <c r="U6" s="4">
+        <v>0</v>
+      </c>
+      <c r="V6" s="4">
+        <v>0</v>
+      </c>
+      <c r="W6" s="4">
+        <v>0</v>
+      </c>
+      <c r="X6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:55">
+      <c r="A7" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4">
+        <v>0</v>
+      </c>
+      <c r="S7" s="4">
+        <v>0</v>
+      </c>
+      <c r="T7" s="4">
+        <v>0</v>
+      </c>
+      <c r="U7" s="4">
+        <v>0</v>
+      </c>
+      <c r="V7" s="4">
+        <v>0</v>
+      </c>
+      <c r="W7" s="4">
+        <v>0</v>
+      </c>
+      <c r="X7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:55">
+      <c r="A8" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4">
+        <v>0</v>
+      </c>
+      <c r="V8" s="4">
+        <v>0</v>
+      </c>
+      <c r="W8" s="4">
+        <v>0</v>
+      </c>
+      <c r="X8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:55">
+      <c r="A9" t="s">
+        <v>86</v>
       </c>
       <c r="B9">
         <v>999</v>
@@ -1560,9 +3762,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>12</v>
+    <row r="10" spans="1:55">
+      <c r="A10" t="s">
+        <v>87</v>
       </c>
       <c r="B10">
         <v>999</v>
@@ -1667,9 +3869,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>13</v>
+    <row r="11" spans="1:55">
+      <c r="A11" t="s">
+        <v>88</v>
       </c>
       <c r="B11">
         <v>999</v>
@@ -1774,9 +3976,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>14</v>
+    <row r="12" spans="1:55">
+      <c r="A12" t="s">
+        <v>89</v>
       </c>
       <c r="B12">
         <v>999</v>
@@ -1881,9 +4083,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>15</v>
+    <row r="13" spans="1:55">
+      <c r="A13" t="s">
+        <v>90</v>
       </c>
       <c r="B13">
         <v>999</v>
@@ -1988,9 +4190,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>16</v>
+    <row r="14" spans="1:55">
+      <c r="A14" t="s">
+        <v>91</v>
       </c>
       <c r="B14">
         <v>999</v>
@@ -2095,223 +4297,223 @@
         <v>999</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="6">
-        <v>0</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0</v>
-      </c>
-      <c r="D15" s="6">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0</v>
-      </c>
-      <c r="G15" s="6">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6">
-        <v>0</v>
-      </c>
-      <c r="I15" s="6">
-        <v>0</v>
-      </c>
-      <c r="J15" s="6">
-        <v>0</v>
-      </c>
-      <c r="K15" s="6">
-        <v>0</v>
-      </c>
-      <c r="L15" s="6">
-        <v>0</v>
-      </c>
-      <c r="M15" s="6">
-        <v>0</v>
-      </c>
-      <c r="N15" s="6">
-        <v>0</v>
-      </c>
-      <c r="O15" s="6">
-        <v>0</v>
-      </c>
-      <c r="P15" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="6">
-        <v>0</v>
-      </c>
-      <c r="R15" s="6">
-        <v>0</v>
-      </c>
-      <c r="S15" s="6">
-        <v>0</v>
-      </c>
-      <c r="T15" s="6">
-        <v>0</v>
-      </c>
-      <c r="U15" s="6">
-        <v>0</v>
-      </c>
-      <c r="V15" s="6">
-        <v>0</v>
-      </c>
-      <c r="W15" s="6">
-        <v>0</v>
-      </c>
-      <c r="X15" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="6">
-        <v>0</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0</v>
-      </c>
-      <c r="F16" s="6">
-        <v>0</v>
-      </c>
-      <c r="G16" s="6">
-        <v>0</v>
-      </c>
-      <c r="H16" s="6">
-        <v>0</v>
-      </c>
-      <c r="I16" s="6">
-        <v>0</v>
-      </c>
-      <c r="J16" s="6">
-        <v>0</v>
-      </c>
-      <c r="K16" s="6">
-        <v>0</v>
-      </c>
-      <c r="L16" s="6">
-        <v>0</v>
-      </c>
-      <c r="M16" s="6">
-        <v>0</v>
-      </c>
-      <c r="N16" s="6">
-        <v>0</v>
-      </c>
-      <c r="O16" s="6">
-        <v>0</v>
-      </c>
-      <c r="P16" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="6">
-        <v>0</v>
-      </c>
-      <c r="R16" s="6">
-        <v>0</v>
-      </c>
-      <c r="S16" s="6">
-        <v>0</v>
-      </c>
-      <c r="T16" s="6">
-        <v>0</v>
-      </c>
-      <c r="U16" s="6">
-        <v>0</v>
-      </c>
-      <c r="V16" s="6">
-        <v>0</v>
-      </c>
-      <c r="W16" s="6">
-        <v>0</v>
-      </c>
-      <c r="X16" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI16" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>19</v>
+    <row r="15" spans="1:55">
+      <c r="A15" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="4">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4">
+        <v>0</v>
+      </c>
+      <c r="P15" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>0</v>
+      </c>
+      <c r="R15" s="4">
+        <v>0</v>
+      </c>
+      <c r="S15" s="4">
+        <v>0</v>
+      </c>
+      <c r="T15" s="4">
+        <v>0</v>
+      </c>
+      <c r="U15" s="4">
+        <v>0</v>
+      </c>
+      <c r="V15" s="4">
+        <v>0</v>
+      </c>
+      <c r="W15" s="4">
+        <v>0</v>
+      </c>
+      <c r="X15" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:55">
+      <c r="A16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="4">
+        <v>0</v>
+      </c>
+      <c r="C16" s="4">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>0</v>
+      </c>
+      <c r="R16" s="4">
+        <v>0</v>
+      </c>
+      <c r="S16" s="4">
+        <v>0</v>
+      </c>
+      <c r="T16" s="4">
+        <v>0</v>
+      </c>
+      <c r="U16" s="4">
+        <v>0</v>
+      </c>
+      <c r="V16" s="4">
+        <v>0</v>
+      </c>
+      <c r="W16" s="4">
+        <v>0</v>
+      </c>
+      <c r="X16" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:35">
+      <c r="A17" t="s">
+        <v>94</v>
       </c>
       <c r="B17">
         <v>999</v>
@@ -2416,9 +4618,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>20</v>
+    <row r="18" spans="1:35">
+      <c r="A18" t="s">
+        <v>95</v>
       </c>
       <c r="B18">
         <v>999</v>
@@ -2523,9 +4725,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>21</v>
+    <row r="19" spans="1:35">
+      <c r="A19" t="s">
+        <v>96</v>
       </c>
       <c r="B19">
         <v>999</v>
@@ -2630,9 +4832,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>22</v>
+    <row r="20" spans="1:35">
+      <c r="A20" t="s">
+        <v>97</v>
       </c>
       <c r="B20">
         <v>999</v>
@@ -2737,9 +4939,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>23</v>
+    <row r="21" spans="1:35">
+      <c r="A21" t="s">
+        <v>98</v>
       </c>
       <c r="B21">
         <v>999</v>
@@ -2844,9 +5046,9 @@
         <v>999</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>24</v>
+    <row r="22" spans="1:35">
+      <c r="A22" t="s">
+        <v>99</v>
       </c>
       <c r="B22">
         <v>999</v>
@@ -2954,4 +5156,175 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B4E34F3-CC89-4669-8AAD-EA6F9A01F9A0}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{829479C9-386B-4EF8-BBC4-61E15B3416DF}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60B28B12-AC1F-4A73-A7ED-EFB69E6AD42D}"/>
 </file>